--- a/artfynd/A 40450-2025 artfynd.xlsx
+++ b/artfynd/A 40450-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1092,53 +1092,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133015051</v>
+        <v>137397516</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storbrännan, Storbrännan, Ång</t>
+          <t>Lidgatu, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598369</v>
+        <v>598577</v>
       </c>
       <c r="R6" t="n">
-        <v>7033086</v>
+        <v>7033192</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1162,12 +1157,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,24 +1187,24 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133015051</t>
+          <t>https://artportalen.se/Sighting/137397516</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133015518</v>
+        <v>133015051</v>
       </c>
       <c r="B7" t="n">
         <v>57972</v>
@@ -1230,19 +1235,19 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+          <t>Storbrännan, Storbrännan, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598589</v>
+        <v>598369</v>
       </c>
       <c r="R7" t="n">
-        <v>7033242</v>
+        <v>7033086</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1299,6 +1304,113 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133015051</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133015518</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Jättjärnbäcken, Jättjärnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>598589</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7033242</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/133015518</t>
         </is>
@@ -1312,6 +1424,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40450-2025 artfynd.xlsx
+++ b/artfynd/A 40450-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>137397516</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40450-2025 artfynd.xlsx
+++ b/artfynd/A 40450-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>137397516</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40450-2025 artfynd.xlsx
+++ b/artfynd/A 40450-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>137397516</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 40450-2025 artfynd.xlsx
+++ b/artfynd/A 40450-2025 artfynd.xlsx
@@ -1095,7 +1095,7 @@
         <v>137397516</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
